--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
   <si>
     <t>Year</t>
   </si>
@@ -497,8 +497,8 @@
       <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="s">
-        <v>4</v>
+      <c r="D8">
+        <v>31.8</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -525,8 +525,8 @@
       <c r="C10">
         <v>9</v>
       </c>
-      <c r="D10" t="s">
-        <v>4</v>
+      <c r="D10">
+        <v>22.4</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -623,8 +623,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17">
-        <v>26.2</v>
+      <c r="D17" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +637,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18">
-        <v>24.3</v>
+      <c r="D18" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +651,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19">
-        <v>28.8</v>
+      <c r="D19" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +665,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20">
-        <v>31.2</v>
+      <c r="D20" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +679,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21">
-        <v>25.3</v>
+      <c r="D21" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -763,8 +763,8 @@
       <c r="C27">
         <v>26</v>
       </c>
-      <c r="D27" t="s">
-        <v>4</v>
+      <c r="D27">
+        <v>31.9</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -791,8 +791,8 @@
       <c r="C29">
         <v>28</v>
       </c>
-      <c r="D29" t="s">
-        <v>4</v>
+      <c r="D29">
+        <v>22.3</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -819,8 +819,8 @@
       <c r="C31">
         <v>30</v>
       </c>
-      <c r="D31" t="s">
-        <v>4</v>
+      <c r="D31">
+        <v>29.1</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -1043,8 +1043,8 @@
       <c r="C47">
         <v>15</v>
       </c>
-      <c r="D47" t="s">
-        <v>4</v>
+      <c r="D47">
+        <v>31</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -1057,8 +1057,8 @@
       <c r="C48">
         <v>16</v>
       </c>
-      <c r="D48" t="s">
-        <v>4</v>
+      <c r="D48">
+        <v>22.9</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -1071,8 +1071,8 @@
       <c r="C49">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
-        <v>4</v>
+      <c r="D49">
+        <v>31.4</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -1113,8 +1113,8 @@
       <c r="C52">
         <v>20</v>
       </c>
-      <c r="D52" t="s">
-        <v>4</v>
+      <c r="D52">
+        <v>28.6</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -1169,8 +1169,8 @@
       <c r="C56">
         <v>24</v>
       </c>
-      <c r="D56" t="s">
-        <v>4</v>
+      <c r="D56">
+        <v>28.3</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -1183,8 +1183,8 @@
       <c r="C57">
         <v>25</v>
       </c>
-      <c r="D57" t="s">
-        <v>4</v>
+      <c r="D57">
+        <v>21.5</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -1225,8 +1225,8 @@
       <c r="C60">
         <v>28</v>
       </c>
-      <c r="D60" t="s">
-        <v>4</v>
+      <c r="D60">
+        <v>29.3</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -1253,8 +1253,8 @@
       <c r="C62">
         <v>30</v>
       </c>
-      <c r="D62" t="s">
-        <v>4</v>
+      <c r="D62">
+        <v>24.7</v>
       </c>
     </row>
   </sheetData>

--- a/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_15h00_timeseries.xlsx
+++ b/results/04_final_refined_daily_hydroclimate_data/203/Dry_bulb_temp_15h00_timeseries.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Year</t>
   </si>
@@ -26,9 +26,6 @@
   </si>
   <si>
     <t>Dry_bulb_temp_15h00</t>
-  </si>
-  <si>
-    <t>NaN</t>
   </si>
 </sst>
 </file>
@@ -623,8 +620,8 @@
       <c r="C17">
         <v>16</v>
       </c>
-      <c r="D17" t="s">
-        <v>4</v>
+      <c r="D17">
+        <v>26.2</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -637,8 +634,8 @@
       <c r="C18">
         <v>17</v>
       </c>
-      <c r="D18" t="s">
-        <v>4</v>
+      <c r="D18">
+        <v>24.3</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -651,8 +648,8 @@
       <c r="C19">
         <v>18</v>
       </c>
-      <c r="D19" t="s">
-        <v>4</v>
+      <c r="D19">
+        <v>28.8</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -665,8 +662,8 @@
       <c r="C20">
         <v>19</v>
       </c>
-      <c r="D20" t="s">
-        <v>4</v>
+      <c r="D20">
+        <v>31.2</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -679,8 +676,8 @@
       <c r="C21">
         <v>20</v>
       </c>
-      <c r="D21" t="s">
-        <v>4</v>
+      <c r="D21">
+        <v>25.3</v>
       </c>
     </row>
     <row r="22" spans="1:4">
